--- a/aq_files/0091.xlsx
+++ b/aq_files/0091.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>A researcher selects 50 students from a list of 500 using a random number generator. What type of sampling is used?</t>
-  </si>
-  <si>
-    <t>A teacher writes all student names on slips of paper, mixes them in a box, and draws 10 names. Which sampling method is this?</t>
-  </si>
-  <si>
-    <t>A company uses a computer program to randomly select 100 customers from its database. Identify the sampling technique.</t>
-  </si>
-  <si>
-    <t>A lottery system is used to choose 5 winners from 200 participants. What type of sampling is being applied?</t>
-  </si>
-  <si>
-    <t>A scientist randomly selects 20 plants from a field of 200 plants for study. What sampling method is this?</t>
-  </si>
-  <si>
-    <t>A school selects students by assigning numbers and using a random number table. Which sampling method is used?</t>
-  </si>
-  <si>
-    <t>A survey randomly picks households from a complete list of households in a town. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A researcher ensures every individual in a population has an equal chance of being selected. What sampling method is this?</t>
-  </si>
-  <si>
-    <t>A company randomly selects 30 employees from its full employee list using software. What type of sampling is used?</t>
-  </si>
-  <si>
-    <t>A researcher uses a lottery method to select 15 participants from a group of 150 people. Identify the sampling type.</t>
-  </si>
-  <si>
-    <t>A study selects patients randomly from a hospital database where every patient has an equal probability of selection. What sampling method is this?</t>
-  </si>
-  <si>
-    <t>A researcher uses random number tables to pick 25 items from a batch of 250. Which sampling method is used?</t>
-  </si>
-  <si>
-    <t>A teacher randomly selects 5 students from a class using slips drawn from a bowl. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A company draws random serial numbers to choose products for quality testing. What sampling method is used?</t>
-  </si>
-  <si>
-    <t>A researcher uses a computerized random selection tool to pick survey respondents. Which sampling method is this?</t>
-  </si>
-  <si>
-    <t>A study selects 40 voters randomly from an electoral list. What type of sampling is applied?</t>
-  </si>
-  <si>
-    <t>A lab technician randomly picks 10 samples from a batch of 100 samples. Identify the sampling method.</t>
-  </si>
-  <si>
-    <t>A researcher selects names randomly from a complete list without any grouping or pattern. What sampling method is used?</t>
-  </si>
-  <si>
-    <t>A teacher uses a random app to pick students for answering questions in class. Which sampling method is this?</t>
-  </si>
-  <si>
-    <t>A company ensures that each product in a production line has an equal chance of being selected for inspection. What type of sampling is this?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,1169 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sales_ID,Sales_Date,Year,Quarter,Month,Month_Name,Week,Day_Name,Region,State,City,Product_Category,Product_SubCategory,Product_Name,Sales_Amount,Profit,Quantity,Discount,Unit_Price,Cost,Shipping_Cost,Tax,Payment_Method,Customer_ID,Customer_Name,Customer_Email,Customer_Phone,Customer_Address,Customer_City,Customer_State,Customer_Zip,Customer_Segment,Membership_Level,Order_Priority,Shipping_Mode,Delivery_Status,Return_Status,Marketing_Channel,Sales_Rep</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10001,2024-01-05,2024,Q1,1,January,1,Monday,North,Illinois,Chicago,Electronics,Computers,MacBook Pro,1299.99,389.99,1,0.05,1299.99,910.00,15.00,78.00,Credit Card,CUST-001,John Smith,john.smith@email.com,555-0101,123 Main St,Chicago,Illinois,60601,Corporate,Gold,High,Standard,Delivered,FALSE,Email,Alice Johnson</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10002,2024-01-05,2024,Q1,1,January,1,Monday,North,Illinois,Chicago,Electronics,Accessories,Magic Mouse,79.99,23.99,3,0.10,79.99,56.00,8.50,4.80,PayPal,CUST-001,John Smith,john.smith@email.com,555-0101,123 Main St,Chicago,Illinois,60601,Corporate,Gold,Medium,Express,Delivered,FALSE,Email,Alice Johnson</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10003,2024-01-06,2024,Q1,1,January,1,Tuesday,South,Texas,Houston,Clothing,Mens,Designer Jeans,89.99,26.99,2,0.00,44.99,63.00,12.00,5.40,Debit Card,CUST-002,Sarah Lee,sarah.lee@email.com,555-0102,456 Oak Ave,Houston,Texas,77001,Consumer,Silver,Medium,Standard,Delivered,FALSE,Social Media,Bob Williams</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10004,2024-01-06,2024,Q1,1,January,1,Tuesday,South,Texas,Austin,Electronics,Monitors,27-inch Monitor,299.99,89.99,1,0.15,299.99,210.00,18.00,18.00,Credit Card,CUST-003,Michael Brown,michael.b@email.com,555-0103,789 Pine St,Austin,Texas,78701,Consumer,Bronze,High,Express,Delivered,FALSE,Search Engine,Bob Williams</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10005,2024-01-07,2024,Q1,1,January,1,Wednesday,East,New York,New York,Furniture,Chairs,Executive Chair,399.99,119.99,2,0.05,199.99,280.00,22.00,24.00,Credit Card,CUST-004,Emily Davis,emily.d@email.com,555-0104,321 Elm St,New York,New York,10001,Corporate,Platinum,High,Standard,Delivered,FALSE,Direct Mail,Carol Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10006,2024-01-07,2024,Q1,1,January,1,Wednesday,East,New York,Buffalo,Electronics,Keyboards,Mechanical Keyboard,89.99,26.99,2,0.10,44.99,63.00,10.00,5.40,PayPal,CUST-005,David Wilson,david.w@email.com,555-0105,654 Maple Ave,Buffalo,New York,14201,Consumer,Bronze,Low,Standard,Delayed,FALSE,Social Media,Carol Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10007,2024-01-08,2024,Q1,1,January,2,Thursday,West,California,Los Angeles,Clothing,Womens,Leather Jacket,199.99,59.99,1,0.20,199.99,140.00,15.00,12.00,Debit Card,CUST-006,Lisa Anderson,lisa.a@email.com,555-0106,987 Cedar Ln,Los Angeles,California,90001,Home Office,Gold,Medium,Express,Delivered,FALSE,Email,David Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10008,2024-01-08,2024,Q1,1,January,2,Thursday,West,California,San Francisco,Electronics,Tablets,iPad,499.99,149.99,1,0.05,499.99,350.00,20.00,30.00,Credit Card,CUST-007,Robert Taylor,robert.t@email.com,555-0107,147 Birch St,San Francisco,California,94101,Corporate,Gold,High,Standard,Delivered,FALSE,Search Engine,David Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10009,2024-01-09,2024,Q1,1,January,2,Friday,North,Illinois,Chicago,Furniture,Lighting,Floor Lamp,79.99,23.99,2,0.00,39.99,56.00,12.00,4.80,PayPal,CUST-008,Jennifer Martinez,jennifer.m@email.com,555-0108,258 Spruce Ave,Chicago,Illinois,60602,Consumer,Silver,Low,Standard,Delivered,FALSE,Email,Alice Johnson</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10010,2024-01-09,2024,Q1,1,January,2,Friday,North,Michigan,Detroit,Clothing,Mens,Running Shoes,69.99,20.99,1,0.10,69.99,49.00,10.00,4.20,Debit Card,CUST-009,William Brown,william.b@email.com,555-0109,369 Walnut St,Detroit,Michigan,48201,Consumer,Bronze,Medium,Express,Delivered,TRUE,Social Media,Alice Johnson</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10011,2024-01-10,2024,Q1,1,January,2,Saturday,South,Texas,Dallas,Electronics,Computers,Gaming Laptop,1299.99,389.99,1,0.15,1299.99,910.00,25.00,78.00,Credit Card,CUST-010,Patricia Davis,patricia.d@email.com,555-0110,741 Cherry Ln,Dallas,Texas,75201,Corporate,Platinum,High,Standard,Delivered,FALSE,Direct Mail,Bob Williams</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10012,2024-01-10,2024,Q1,1,January,2,Saturday,East,Pennsylvania,Philadelphia,Electronics,Audio,Headphones,149.99,44.99,2,0.05,74.99,105.00,12.00,9.00,PayPal,CUST-011,Michael Miller,michael.m@email.com,555-0111,852 Dogwood Dr,Philadelphia,Pennsylvania,19101,Consumer,Silver,Medium,Express,Delivered,FALSE,Social Media,Carol Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10013,2024-01-11,2024,Q1,1,January,2,Sunday,West,California,San Diego,Clothing,Womens,Wool Coat,189.99,56.99,1,0.20,189.99,133.00,15.00,11.40,Debit Card,CUST-012,Linda Wilson,linda.w@email.com,555-0112,963 Magnolia Rd,San Diego,California,92101,Home Office,Gold,Medium,Standard,Delivered,FALSE,Email,David Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10014,2024-01-11,2024,Q1,1,January,2,Sunday,North,Ohio,Columbus,Furniture,Storage,Bookshelf,159.99,47.99,1,0.10,159.99,112.00,18.00,9.60,Credit Card,CUST-013,Richard Moore,richard.m@email.com,555-0113,159 Cypress Ct,Columbus,Ohio,43201,Corporate,Silver,Medium,Standard,Delivered,FALSE,Search Engine,Alice Johnson</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10015,2024-01-12,2024,Q1,1,January,2,Monday,South,Florida,Miami,Electronics,Phones,Smartphone,699.99,209.99,2,0.05,349.99,490.00,12.00,42.00,Credit Card,CUST-014,Susan Taylor,susan.t@email.com,555-0114,753 Palm Ave,Miami,Florida,33101,Consumer,Bronze,High,Express,Delivered,FALSE,Social Media,Bob Williams</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10016,2024-01-12,2024,Q1,1,January,2,Monday,East,New York,New York,Clothing,Mens,Dress Shirt,59.99,17.99,3,0.00,20.00,42.00,10.00,3.60,PayPal,CUST-015,Thomas Anderson,thomas.a@email.com,555-0115,951 Holly St,New York,New York,10002,Corporate,Gold,Medium,Standard,Delivered,FALSE,Email,Carol Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10017,2024-01-13,2024,Q1,1,January,2,Tuesday,West,Oregon,Portland,Electronics,Storage,External SSD,99.99,29.99,1,0.10,99.99,70.00,8.50,6.00,Debit Card,CUST-016,Jessica Thomas,jessica.t@email.com,555-0116,852 Fir Ln,Portland,Oregon,97201,Consumer,Silver,Low,Standard,Delivered,FALSE,Social Media,David Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10018,2024-01-13,2024,Q1,1,January,2,Tuesday,North,Illinois,Chicago,Clothing,Womens,Hoodie,49.99,14.99,2,0.05,25.00,35.00,12.00,3.00,PayPal,CUST-017,Charles Jackson,charles.j@email.com,555-0117,753 Spruce Ave,Chicago,Illinois,60603,Consumer,Bronze,Medium,Express,Delivered,TRUE,Email,Alice Johnson</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10019,2024-01-14,2024,Q1,1,January,2,Wednesday,South,Texas,Austin,Furniture,Desks,Gaming Desk,349.99,104.99,1,0.15,349.99,245.00,25.00,21.00,Credit Card,CUST-018,Sarah White,sarah.w@email.com,555-0118,951 Willow Dr,Austin,Texas,78702,Corporate,Platinum,High,Standard,Delivered,FALSE,Direct Mail,Bob Williams</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>SALE-10020,2024-01-14,2024,Q1,1,January,2,Wednesday,East,Massachusetts,Boston,Electronics,Accessories,Webcam,79.99,23.99,2,0.10,39.99,56.00,8.50,4.80,PayPal,CUST-019,Daniel Harris,daniel.h@email.com,555-0119,357 Ash St,Boston,Massachusetts,02101,Home Office,Gold,Medium,Express,Delivered,FALSE,Email,Carol Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>21,ORD-1021,2024-02-01,2024-02-01 09:00:00,Electronics|Docks|Docking,Docking Station,Electronics,Docks,129.99,1,0%,38.99,"Clark, Matthew",matthew.c@email.com,555-0120,"159 Beech Court",Seattle WA 98101,USA,WC,Active,N,"",2024-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>22,ORD-1022,2024-02-01,2024-02-01 10:45:00,Clothing|Mens|Outerwear,Winter Parka,Clothing,Mens,179.99,1,5%,53.99,"Lewis, Amanda",amanda.l@email.com,555-0121,"753 Poplar Avenue",Minneapolis MN 55401,USA,NW,Active,N,"",2024-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>23,ORD-1023,2024-02-02,2024-02-02 13:30:00,Furniture|Desks|Office,Office Desk,Furniture,Desks,449.99,1,10%,134.99,"Walker, James",james.w@email.com,555-0122,"951 Cedar Street",Orlando FL 32801,USA,SW,Active,N,"",2024-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>24,ORD-1024,2024-02-02,2024-02-02 15:20:00,Electronics|Cables|USB,USB-C Hub,Electronics,Cables,39.99,3,0%,11.99,"Hall, Betty",betty.h@email.com,555-0123,"357 Maple Lane",Newark NJ 07101,USA,NE,Active,N,"",2024-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>25,ORD-1025,2024-02-03,2024-02-03 08:15:00,Clothing|Mens|Blazers,Casual Blazer,Clothing,Mens,149.99,1,15%,44.99,"Young, Kevin",kevin.y@email.com,555-0124,"753 Elm Drive",Los Angeles CA 90002,USA,WC,Active,N,"",2024-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>26,ORD-1026,2024-02-03,2024-02-03 11:45:00,Electronics|Accessories|Mice,Gaming Mouse,Electronics,Accessories,59.99,2,10%,17.99,"Allen, Nancy",nancy.a@email.com,555-0125,"159 Oak Court",Indianapolis IN 46201,USA,NW,Returned,Y,"Defective product - replacement needed",2024-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>27,ORD-1027,2024-02-04,2024-02-04 09:30:00,Electronics|Printers|Laser,Laser Printer,Electronics,Printers,199.99,1,5%,59.99,"King, Edward",edward.k@email.com,555-0126,"357 Pine Avenue",Atlanta GA 30301,USA,SW,Active,N,"",2024-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>28,ORD-1028,2024-02-04,2024-02-04 14:00:00,Furniture|Chairs|Lounge,Lounge Chair,Furniture,Chairs,279.99,1,20%,83.99,"Wright, Donna",donna.w@email.com,555-0127,"951 Birch Street",Richmond VA 23201,USA,NE,Active,N,"",2024-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>29,ORD-1029,2024-02-05,2024-02-05 10:15:00,Electronics|Batteries|Power Banks,Power Bank,Electronics,Batteries,49.99,4,0%,14.99,"Lopez, George",george.l@email.com,555-0128,"753 Cedar Avenue",Phoenix AZ 85001,USA,WC,Active,N,"",2024-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>30,ORD-1030,2024-02-05,2024-02-05 12:30:00,Clothing|Accessories|Scarves,Wool Scarf,Clothing,Accessories,24.99,5,10%,7.49,"Hill, Sandra",sandra.h@email.com,555-0129,"159 Walnut Lane",Milwaukee WI 53201,USA,NW,Active,N,"",2024-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>31,ORD-1031,2024-02-06,2024-02-06 13:45:00,Electronics|Audio|Headphones,Gaming Headset,Electronics,Audio,119.99,1,5%,35.99,"Scott, Brian",brian.s@email.com,555-0130,"357 Dogwood Drive",Houston TX 77002,USA,SW,Active,N,"",2024-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>32,ORD-1032,2024-02-06,2024-02-06 15:30:00,Furniture|Storage|Nightstands,Night Stand,Furniture,Storage,69.99,2,10%,20.99,"Adams, Carolyn",carolyn.a@email.com,555-0131,"753 Magnolia Road",Rochester NY 14601,USA,NE,Active,N,"",2024-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>33,ORD-1033,2024-02-07,2024-02-07 09:20:00,Clothing|Mens|Footwear,Athletic Shoes,Clothing,Mens,109.99,1,15%,32.99,"Baker, Frank",frank.b@email.com,555-0132,"159 Cypress Court",San Jose CA 95101,USA,WC,Active,N,"",2024-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>34,ORD-1034,2024-02-07,2024-02-07 11:00:00,Electronics|Wearables|Watches,Smart Watch,Electronics,Wearables,199.99,1,5%,59.99,"Gonzalez, Ruth",ruth.g@email.com,555-0133,"357 Palm Avenue",St Louis MO 63101,USA,NW,Active,N,"",2024-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>35,ORD-1035,2024-02-08,2024-02-08 14:15:00,Electronics|Audio|Speakers,Bluetooth Speaker,Electronics,Audio,79.99,2,10%,23.99,"Nelson, Peter",peter.n@email.com,555-0134,"951 Holly Street",Tampa FL 33601,USA,SW,Active,N,"",2024-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>36,ORD-1036,2024-02-08,2024-02-08 16:45:00,Clothing|Womens|Sweaters,Cashmere Sweater,Clothing,Womens,99.99,1,0%,29.99,"Carter, Kimberly",kimberly.c@email.com,555-0135,"753 Fir Lane",Pittsburgh PA 15201,USA,NE,Returned,Y,"Quality issue - fabric defect",2024-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>37,ORD-1037,2024-02-09,2024-02-09 10:30:00,Furniture|Storage|Bookcases,Bookshelf,Furniture,Storage,129.99,1,5%,38.99,"Mitchell, Steven",steven.m@email.com,555-0136,"159 Spruce Avenue",Eugene OR 97401,USA,WC,Active,N,"",2024-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>38,ORD-1038,2024-02-09,2024-02-09 12:00:00,Electronics|Networking|Routers,Mesh Router,Electronics,Networking,99.99,1,10%,29.99,"Perez, Laura",laura.p@email.com,555-0137,"357 Willow Drive",Des Moines IA 50301,USA,NW,Active,N,"",2024-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>39,ORD-1039,2024-02-10,2024-02-10 09:45:00,Clothing|Mens|Polos,Golf Polo,Clothing,Mens,44.99,3,15%,13.49,"Roberts, Paul",paul.r@email.com,555-0138,"753 Ash Street",San Antonio TX 78201,USA,SW,Active,N,"",2024-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>40,ORD-1040,2024-02-10,2024-02-10 13:15:00,Electronics|Components|Graphics,Graphics Card,Electronics,Components,499.99,1,20%,149.99,"Turner, Mary",mary.t@email.com,555-0139,"159 Beech Court",Spokane WA 99201,USA,WC,Active,N,"",2024-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>41,ORD-1041,2024-03-01,2024-03-01 10:00:00,Electronics|Computers|Desktops,Desktop PC,Electronics,Computers,999.99,1,5%,299.99,"Phillips, Daniel",daniel.p@email.com,555-0140,"357 Poplar Avenue",Chicago IL 60604,USA,NW,Active,N,"",2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>42,ORD-1042,2024-03-01,2024-03-01 11:30:00,Clothing|Womens|Bottoms,Yoga Pants,Clothing,Womens,49.99,2,0%,14.99,"Campbell, Lisa",lisa.c@email.com,555-0141,"753 Cedar Street",Austin TX 78703,USA,SW,Active,N,"",2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>43,ORD-1043,2024-03-02,2024-03-02 14:45:00,Furniture|Tables|Coffee,Coffee Table,Furniture,Tables,249.99,1,10%,74.99,"Parker, Ronald",ronald.p@email.com,555-0142,"951 Maple Lane",New York NY 10003,USA,NE,Active,N,"",2024-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>44,ORD-1044,2024-03-02,2024-03-02 16:20:00,Electronics|Smart Home|Speakers,Smart Speaker,Electronics,Smart Home,89.99,2,0%,26.99,"Evans, Deborah",deborah.e@email.com,555-0143,"357 Elm Drive",Los Angeles CA 90003,USA,WC,Active,N,"",2024-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>45,ORD-1045,2024-03-03,2024-03-03 08:30:00,Clothing|Accessories|Hats,Baseball Cap,Clothing,Accessories,19.99,4,5%,5.99,"Edwards, Joseph",joseph.e@email.com,555-0144,"159 Oak Court",Detroit MI 48202,USA,NW,Active,N,"",2024-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>46,ORD-1046,2024-03-03,2024-03-03 12:15:00,Electronics|Drones|Quadcopter,Quadcopter,Electronics,Drones,349.99,1,10%,104.99,"Collins, Barbara",barbara.c@email.com,555-0145,"753 Pine Avenue",Miami FL 33102,USA,SW,Active,N,"",2024-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>47,ORD-1047,2024-03-04,2024-03-04 09:45:00,Furniture|Decor|Mirrors,Wall Mirror,Furniture,Decor,59.99,2,0%,17.99,"Stewart, Mark",mark.s@email.com,555-0146,"951 Birch Street",Philadelphia PA 19102,USA,NE,Active,N,"",2024-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>48,ORD-1048,2024-03-04,2024-03-04 13:30:00,Clothing|Mens|Shirts,Flannel Shirt,Clothing,Mens,49.99,2,10%,14.99,"Morris, Carol",carol.m@email.com,555-0147,"357 Cedar Avenue",Portland OR 97202,USA,WC,Active,N,"",2024-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>49,ORD-1049,2024-03-05,2024-03-05 10:30:00,Electronics|Streaming|Sticks,Streaming Stick,Electronics,Streaming,29.99,3,5%,8.99,"Rogers, Raymond",raymond.r@email.com,555-0148,"753 Walnut Lane",Columbus OH 43202,USA,NW,Returned,Y,"Not working properly - defective",2024-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>50,ORD-1050,2024-03-05,2024-03-05 14:00:00,Clothing|Womens|Bottoms,Leggings,Clothing,Womens,29.99,4,0%,8.99,"Reed, Anna",anna.r@email.com,555-0149,"159 Dogwood Drive",Atlanta GA 30302,USA,SW,Active,N,"",2024-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3051,2024-02-11,West,California,Los Angeles,Electronics,Monitors,Ultrawide Monitor,549.99,2,549.98,0.15,22.00,Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3052,2024-02-11,North,Illinois,Chicago,Clothing,Mens,Denim Jacket,89.99,5,224.98,0.10,12.00,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3053,2024-02-12,South,Texas,Houston,Furniture,Chairs,Gaming Chair,299.99,2,299.98,0.05,22.00,Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3054,2024-02-12,East,New York,Buffalo,Electronics,Audio,Portable Speaker,79.99,4,159.98,0.00,10.00,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3055,2024-02-13,West,Washington,Seattle,Clothing,Womens,Rain Jacket,129.99,3,194.98,0.15,12.00,Home Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3056,2024-02-13,North,Minnesota,Minneapolis,Electronics,Storage,Portable SSD,89.99,5,224.98,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3057,2024-02-14,South,Florida,Orlando,Electronics,Phones,Smartphone Case,29.99,15,224.85,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3058,2024-02-14,East,Massachusetts,Boston,Furniture,Lighting,Desk Lamp,59.99,6,179.97,0.05,12.00,Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3059,2024-02-15,West,California,San Diego,Clothing,Accessories,Leather Belt,39.99,8,159.96,0.10,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>ORD-3060,2024-02-15,North,Ohio,Columbus,Electronics,Accessories,Phone Stand,19.99,12,119.94,0.00,8.50,Consumer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>10,Promote Headers,"For CSV file: Home → Use First Row as Headers","Power Query Editor","Ensure first row contains column names; Verify after promotion","Headers promoted correctly"</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>11,Set Data Types,"Change data types: Date columns to Date; Numeric columns to Decimal/Whole Number; Text columns to Text","Power Query Editor","Verify data type conversions; Handle errors; Use locale for dates","All columns have correct data types"</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>26,Apply Consistent Theme,"View → Themes → Select or Create Custom Theme","Report View","Use company colors; Maintain consistency across reports","Theme applied to report"</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>What is Creating Our Initial Project File?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Why is Creating Our Initial Project File important in Creating Our Initial Project File?</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Explain the main workflow of Creating Our Initial Project File.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>Process Understanding</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>List the key components involved in Creating Our Initial Project File.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>Component Awareness</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>How is Creating Our Initial Project File applied in a practical business scenario?</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>Applied Understanding</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What problem does Creating Our Initial Project File help solve?</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>Problem Framing</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Describe the core steps required to complete Creating Our Initial Project File.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>Execution Flow</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>What inputs are typically required before starting Creating Our Initial Project File?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Input Readiness</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>What outputs or results are expected from Creating Our Initial Project File?</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>Output Interpretation</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>How would you validate whether Creating Our Initial Project File was completed correctly?</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>What are common mistakes to avoid while working on Creating Our Initial Project File?</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>Error Awareness</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>How does Creating Our Initial Project File improve decision-making or outcomes?</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Business Value</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>What assumptions should be checked before using Creating Our Initial Project File?</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>Assumption Checking</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>How would you explain Creating Our Initial Project File to a beginner?</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Concept Simplification</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>What metrics or indicators are useful when evaluating Creating Our Initial Project File?</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>How does Creating Our Initial Project File connect with earlier modules in the course?</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Module Integration</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>What are the prerequisites for learning Creating Our Initial Project File?</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Course AIE | BIA - 119/Data Transformation Techniques/Creating Our Initial Project File</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>